--- a/em-new-ship-20261016.xlsx
+++ b/em-new-ship-20261016.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新品备货测算" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需发货清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="备货清单" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="零动销新品" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -40,7 +40,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <sz val="9"/>
@@ -48,7 +48,7 @@
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -76,7 +76,7 @@
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -580,7 +580,7 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7.5" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
@@ -589,27 +589,27 @@
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>发动机支架 新品备货测算 ｜ 库存快照 2026-10-16 ｜ 销量=到货后约1个月（70个新品）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
+          <t>发动机支架 新品【备货】测算 ｜ 库存快照 2026-10-16 ｜ 70个新品（商品状态=推新）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径: 月销量 = 新品到货后约1个月实际销量（文件48）｜ 目标库存 = 月销量 × 6（库销比=6）｜ 库存 = 可用库存 + 头程在途 ｜ 建议发货 = max(0, 目标库存 − 库存) ｜ 补货周期 97天 · 安全 21天</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>口径: 月销量 = 新品到货后约1个月实际销量 ｜ 备货数量 = 目标库存(月销×6) + 补货周期(97天)内消耗 − (可用库存 + 头程在途) ｜ 补货周期 97天(采购30+海运60+入仓7) · 安全库存 21天 ｜ ★本地仓无库存，本表为向工厂下单量</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -689,22 +689,22 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>建议发货量</t>
+          <t>97天周期消耗</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
+          <t>备货数量</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
           <t>采购单价</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>需发货金额</t>
-        </is>
-      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>需发货箱数</t>
+          <t>备货金额</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -767,17 +767,17 @@
       <c r="O5" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="P5" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q5" s="4" t="n">
+      <c r="P5" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="R5" s="4" t="n">
         <v>145.13</v>
       </c>
-      <c r="R5" s="4" t="n">
-        <v>8272.4</v>
-      </c>
       <c r="S5" s="4" t="n">
-        <v>57</v>
+        <v>13434.2</v>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
@@ -839,17 +839,17 @@
       <c r="O6" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="P6" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q6" s="4" t="n">
+      <c r="P6" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="R6" s="4" t="n">
         <v>219.47</v>
       </c>
-      <c r="R6" s="4" t="n">
-        <v>12509.8</v>
-      </c>
       <c r="S6" s="4" t="n">
-        <v>57</v>
+        <v>20315.6</v>
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
@@ -911,17 +911,17 @@
       <c r="O7" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="P7" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q7" s="4" t="n">
+      <c r="P7" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="R7" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="R7" s="4" t="n">
-        <v>1947</v>
-      </c>
       <c r="S7" s="4" t="n">
-        <v>55</v>
+        <v>3206.1</v>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
@@ -983,17 +983,17 @@
       <c r="O8" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="P8" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q8" s="4" t="n">
+      <c r="P8" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="R8" s="4" t="n">
         <v>84.06999999999999</v>
       </c>
-      <c r="R8" s="4" t="n">
-        <v>4623.8</v>
-      </c>
       <c r="S8" s="4" t="n">
-        <v>55</v>
+        <v>7613.9</v>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
@@ -1055,17 +1055,17 @@
       <c r="O9" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="P9" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q9" s="4" t="n">
+      <c r="P9" s="4" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="R9" s="4" t="n">
         <v>331.86</v>
       </c>
-      <c r="R9" s="4" t="n">
-        <v>14270</v>
-      </c>
       <c r="S9" s="4" t="n">
-        <v>43</v>
+        <v>23927.1</v>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
@@ -1127,17 +1127,17 @@
       <c r="O10" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="P10" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q10" s="4" t="n">
+      <c r="P10" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R10" s="4" t="n">
         <v>192.04</v>
       </c>
-      <c r="R10" s="4" t="n">
-        <v>6145.3</v>
-      </c>
       <c r="S10" s="4" t="n">
-        <v>32</v>
+        <v>10491.8</v>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
@@ -1199,17 +1199,17 @@
       <c r="O11" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="P11" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="4" t="n">
+      <c r="P11" s="4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="R11" s="4" t="n">
         <v>84.06999999999999</v>
       </c>
-      <c r="R11" s="4" t="n">
-        <v>2101.8</v>
-      </c>
       <c r="S11" s="4" t="n">
-        <v>25</v>
+        <v>3732.7</v>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
@@ -1271,17 +1271,17 @@
       <c r="O12" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="P12" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q12" s="4" t="n">
+      <c r="P12" s="4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="R12" s="4" t="n">
         <v>138.05</v>
       </c>
-      <c r="R12" s="4" t="n">
-        <v>3037.1</v>
-      </c>
       <c r="S12" s="4" t="n">
-        <v>22</v>
+        <v>5268.9</v>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
@@ -1343,17 +1343,17 @@
       <c r="O13" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="P13" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q13" s="4" t="n">
+      <c r="P13" s="4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="R13" s="4" t="n">
         <v>155.75</v>
       </c>
-      <c r="R13" s="4" t="n">
-        <v>2959.2</v>
-      </c>
       <c r="S13" s="4" t="n">
-        <v>19</v>
+        <v>5477.2</v>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
@@ -1415,17 +1415,17 @@
       <c r="O14" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="P14" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q14" s="4" t="n">
+      <c r="P14" s="4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="R14" s="4" t="n">
         <v>421.24</v>
       </c>
-      <c r="R14" s="4" t="n">
-        <v>7161.1</v>
-      </c>
       <c r="S14" s="4" t="n">
-        <v>17</v>
+        <v>13971.1</v>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
@@ -1487,17 +1487,17 @@
       <c r="O15" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="P15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q15" s="4" t="n">
+      <c r="P15" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R15" s="4" t="n">
         <v>144.09</v>
       </c>
-      <c r="R15" s="4" t="n">
-        <v>864.5</v>
-      </c>
       <c r="S15" s="4" t="n">
-        <v>6</v>
+        <v>2262.2</v>
       </c>
       <c r="T15" s="9" t="inlineStr">
         <is>
@@ -1559,17 +1559,17 @@
       <c r="O16" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="P16" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="4" t="n">
+      <c r="P16" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="R16" s="4" t="n">
         <v>179.91</v>
       </c>
-      <c r="R16" s="4" t="n">
-        <v>899.5</v>
-      </c>
       <c r="S16" s="4" t="n">
-        <v>5</v>
+        <v>2644.7</v>
       </c>
       <c r="T16" s="9" t="inlineStr">
         <is>
@@ -1631,17 +1631,17 @@
       <c r="O17" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="P17" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="4" t="n">
+      <c r="P17" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="R17" s="4" t="n">
         <v>216.81</v>
       </c>
-      <c r="R17" s="4" t="n">
-        <v>867.2</v>
-      </c>
       <c r="S17" s="4" t="n">
-        <v>4</v>
+        <v>2970.3</v>
       </c>
       <c r="T17" s="9" t="inlineStr">
         <is>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>B0HBB4WFRS</t>
+          <t>B0HBB4L2SL</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO43900</t>
+          <t>OO1EMO45100</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>1EMO4390</t>
+          <t>1EMO4510</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1674,46 +1674,46 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>938.332</v>
+        <v>870.732</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.1818</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>19</v>
+        <v>6.5</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>570</v>
+        <v>195</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>419.47</v>
+        <v>6.5</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0</v>
+        <v>172.41</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0</v>
+        <v>942.5</v>
       </c>
       <c r="T18" s="9" t="inlineStr">
         <is>
@@ -1727,17 +1727,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>B0HBB919W9</t>
+          <t>B0HBBHJGXG</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO51100</t>
+          <t>OO1EMO42200</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1EMO5110</t>
+          <t>1EMO4220</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1746,46 +1746,46 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>522.533</v>
+        <v>394.898</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0476</v>
+        <v>0.1538</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>570</v>
+        <v>210</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>203.54</v>
+        <v>6.5</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0</v>
+        <v>41.64</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="T19" s="9" t="inlineStr">
         <is>
@@ -1799,17 +1799,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>B0HBB4L2SL</t>
+          <t>B0HBB9X8RT</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO45100</t>
+          <t>OO1EMO45300</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1EMO4510</t>
+          <t>1EMO4530</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1818,46 +1818,46 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>234.433</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="4" t="n">
-        <v>870.732</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>195</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>172.41</v>
-      </c>
       <c r="R20" s="4" t="n">
-        <v>0</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0</v>
+        <v>145.9</v>
       </c>
       <c r="T20" s="9" t="inlineStr">
         <is>
@@ -1871,17 +1871,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>B0HBBF5R79</t>
+          <t>B0HBBL8N35</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO41500</t>
+          <t>OO1EMO40800</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1EMO4150</t>
+          <t>1EMO4080</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1893,43 +1893,43 @@
         <v>2</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1068.516</v>
+        <v>1205.598</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="N21" s="4" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="O21" s="4" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>230.97</v>
+        <v>6.5</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0</v>
+        <v>246.9</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="T21" s="9" t="inlineStr">
         <is>
@@ -1943,17 +1943,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>B0HBB7SWFB</t>
+          <t>B0HBB4WFRS</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO39500</t>
+          <t>OO1EMO43900</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1EMO3950</t>
+          <t>1EMO4390</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1965,40 +1965,40 @@
         <v>1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>321.533</v>
+        <v>938.332</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.125</v>
+        <v>0.0312</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>450</v>
+        <v>570</v>
       </c>
       <c r="O22" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0</v>
+        <v>419.47</v>
       </c>
       <c r="S22" s="4" t="n">
         <v>0</v>
@@ -2015,17 +2015,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>B0HBBDG7TV</t>
+          <t>B0HBB919W9</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO42400</t>
+          <t>OO1EMO51100</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1EMO4240</t>
+          <t>1EMO5110</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2037,19 +2037,19 @@
         <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>334.933</v>
+        <v>522.533</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0476</v>
       </c>
       <c r="I23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="K23" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>19</v>
@@ -2064,13 +2064,13 @@
         <v>6</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>115.04</v>
+        <v>0</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0</v>
+        <v>203.54</v>
       </c>
       <c r="S23" s="4" t="n">
         <v>0</v>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>B0HBBB9K9D</t>
+          <t>B0HBBF5R79</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO52400</t>
+          <t>OO1EMO41500</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>1EMO5240</t>
+          <t>1EMO4150</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2106,46 +2106,46 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>589.533</v>
+        <v>1068.516</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>480</v>
+        <v>270</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>246.54</v>
+        <v>0</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0</v>
+        <v>230.97</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0</v>
+        <v>107.8</v>
       </c>
       <c r="T24" s="9" t="inlineStr">
         <is>
@@ -2159,17 +2159,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>B0HB9WBVK5</t>
+          <t>B0HBB7SWFB</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO50300</t>
+          <t>OO1EMO39500</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1EMO5030</t>
+          <t>1EMO3950</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2178,25 +2178,25 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>334.866</v>
+        <v>321.533</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>15</v>
@@ -2205,16 +2205,16 @@
         <v>450</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>38.94</v>
+        <v>0</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="S25" s="4" t="n">
         <v>0</v>
@@ -2231,17 +2231,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>B0HBBHJGXG</t>
+          <t>B0HBBDG7TV</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO42200</t>
+          <t>OO1EMO42400</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1EMO4220</t>
+          <t>1EMO4240</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2250,43 +2250,43 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>394.898</v>
+        <v>334.933</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1538</v>
+        <v>0.0625</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>210</v>
+        <v>570</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>41.64</v>
+        <v>0</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0</v>
+        <v>115.04</v>
       </c>
       <c r="S26" s="4" t="n">
         <v>0</v>
@@ -2303,17 +2303,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>B0HBB485VJ</t>
+          <t>B0HBBB9K9D</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO45500</t>
+          <t>OO1EMO52400</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1EMO4550</t>
+          <t>1EMO5240</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2325,40 +2325,40 @@
         <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>770.433</v>
+        <v>589.533</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="O27" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>291.15</v>
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0</v>
+        <v>246.54</v>
       </c>
       <c r="S27" s="4" t="n">
         <v>0</v>
@@ -2375,17 +2375,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>B0HB9ZK2ZK</t>
+          <t>B0HB9WBVK5</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO51600</t>
+          <t>OO1EMO50300</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1EMO5160</t>
+          <t>1EMO5030</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2394,43 +2394,43 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>489.033</v>
+        <v>334.866</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>209.73</v>
+        <v>0</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0</v>
+        <v>38.94</v>
       </c>
       <c r="S28" s="4" t="n">
         <v>0</v>
@@ -2447,17 +2447,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>B0HBB9C2XG</t>
+          <t>B0HBB485VJ</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO40300</t>
+          <t>OO1EMO45500</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1EMO4030</t>
+          <t>1EMO4550</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2469,40 +2469,40 @@
         <v>1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>736.933</v>
+        <v>770.433</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0476</v>
+        <v>0.05</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>540</v>
+        <v>330</v>
       </c>
       <c r="O29" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>304.42</v>
+        <v>0</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0</v>
+        <v>291.15</v>
       </c>
       <c r="S29" s="4" t="n">
         <v>0</v>
@@ -2519,17 +2519,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>B0HBBHG53J</t>
+          <t>B0HB9ZK2ZK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO50400</t>
+          <t>OO1EMO51600</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>1EMO5040</t>
+          <t>1EMO5160</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2541,40 +2541,40 @@
         <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>656.533</v>
+        <v>489.033</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.0556</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="O30" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>283.19</v>
+        <v>0</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0</v>
+        <v>209.73</v>
       </c>
       <c r="S30" s="4" t="n">
         <v>0</v>
@@ -2591,17 +2591,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>B0HBBJ6YQC</t>
+          <t>B0HBB9C2XG</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO51701</t>
+          <t>OO1EMO40300</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1EMO5170</t>
+          <t>1EMO4030</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2613,40 +2613,40 @@
         <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>509.932</v>
+        <v>736.933</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.04</v>
+        <v>0.0476</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="O31" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>176.99</v>
+        <v>0</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0</v>
+        <v>304.42</v>
       </c>
       <c r="S31" s="4" t="n">
         <v>0</v>
@@ -2663,17 +2663,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>B0HB9Z5MHY</t>
+          <t>B0HBBHG53J</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO53100</t>
+          <t>OO1EMO50400</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1EMO5310</t>
+          <t>1EMO5040</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2685,40 +2685,40 @@
         <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>422.033</v>
+        <v>656.533</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05</v>
+        <v>0.3333</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>19</v>
-      </c>
       <c r="M32" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>570</v>
+        <v>450</v>
       </c>
       <c r="O32" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>153.98</v>
+        <v>0</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0</v>
+        <v>283.19</v>
       </c>
       <c r="S32" s="4" t="n">
         <v>0</v>
@@ -2735,17 +2735,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>B0HBB9X8RT</t>
+          <t>B0HBBJ6YQC</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO45300</t>
+          <t>OO1EMO51701</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1EMO4530</t>
+          <t>1EMO5170</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2757,40 +2757,40 @@
         <v>1</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>234.433</v>
+        <v>509.932</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.04</v>
       </c>
       <c r="I33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J33" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="O33" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>65.34999999999999</v>
+        <v>0</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0</v>
+        <v>176.99</v>
       </c>
       <c r="S33" s="4" t="n">
         <v>0</v>
@@ -2807,17 +2807,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>B0HBB1FHKP</t>
+          <t>B0HB9Z5MHY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO49600</t>
+          <t>OO1EMO53100</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1EMO4960</t>
+          <t>1EMO5310</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2829,40 +2829,40 @@
         <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>496.332</v>
+        <v>422.033</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.05</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>450</v>
+        <v>570</v>
       </c>
       <c r="O34" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>176.99</v>
+        <v>0</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0</v>
+        <v>153.98</v>
       </c>
       <c r="S34" s="4" t="n">
         <v>0</v>
@@ -2879,17 +2879,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>B0HBB98X8B</t>
+          <t>B0HBB1FHKP</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO51500</t>
+          <t>OO1EMO49600</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1EMO5150</t>
+          <t>1EMO4960</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2901,40 +2901,40 @@
         <v>1</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>355.033</v>
+        <v>496.332</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.3333</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
       <c r="O35" s="4" t="n">
         <v>6</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>114.16</v>
+        <v>0</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0</v>
+        <v>176.99</v>
       </c>
       <c r="S35" s="4" t="n">
         <v>0</v>
@@ -2951,17 +2951,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>B0HBB9NPTV</t>
+          <t>B0HBB98X8B</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO44600</t>
+          <t>OO1EMO51500</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1EMO4460</t>
+          <t>1EMO5150</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -2970,43 +2970,43 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>334.866</v>
+        <v>355.033</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0741</v>
+        <v>0.1111</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>270</v>
+        <v>690</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>34.51</v>
+        <v>0</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>0</v>
+        <v>114.16</v>
       </c>
       <c r="S36" s="4" t="n">
         <v>0</v>
@@ -3023,17 +3023,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>B0HBB7TL9G</t>
+          <t>B0HBB9NPTV</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO44200</t>
+          <t>OO1EMO44600</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1EMO4420</t>
+          <t>1EMO4460</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3042,46 +3042,46 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>441.932</v>
+        <v>334.866</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0303</v>
+        <v>0.0741</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>510</v>
+        <v>270</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>145.13</v>
+        <v>0</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>0</v>
+        <v>34.51</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="T37" s="9" t="inlineStr">
         <is>
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>B0HBBL8N35</t>
+          <t>B0HBB7TL9G</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>OO1EMO40800</t>
+          <t>OO1EMO44200</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1EMO4080</t>
+          <t>1EMO4420</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3114,43 +3114,43 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1205.598</v>
+        <v>441.932</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0303</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>240</v>
+        <v>510</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>246.9</v>
+        <v>0</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>0</v>
+        <v>145.13</v>
       </c>
       <c r="S38" s="4" t="n">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>6</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="4" t="n">
         <v>35.81</v>
-      </c>
-      <c r="R39" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="S39" s="4" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -3258,21 +3258,22 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>需发货清单 ｜ 13 个 ASIN ｜ 397 件 ｜ ¥65,659 ｜ 约 397 箱</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>备货清单 ｜ 17 个 ASIN ｜ 合计 703 件 ｜ ¥117,199</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -3310,25 +3311,30 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>建议发货量</t>
+          <t>目标库存</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>97天周期消耗</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>备货数量</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>采购单价</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>需发货金额</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>需发货箱数</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>备货金额</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>缺货等级</t>
         </is>
@@ -3360,19 +3366,22 @@
       <c r="G4" s="11" t="n">
         <v>24.5</v>
       </c>
-      <c r="H4" s="13" t="n">
-        <v>57</v>
+      <c r="H4" s="11" t="n">
+        <v>66</v>
       </c>
       <c r="I4" s="11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="K4" s="11" t="n">
         <v>145.13</v>
       </c>
-      <c r="J4" s="11" t="n">
-        <v>8272.4</v>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="11" t="n">
+        <v>13434.2</v>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>断货高危</t>
         </is>
@@ -3404,19 +3413,22 @@
       <c r="G5" s="11" t="n">
         <v>24.5</v>
       </c>
-      <c r="H5" s="13" t="n">
-        <v>57</v>
+      <c r="H5" s="11" t="n">
+        <v>66</v>
       </c>
       <c r="I5" s="11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="K5" s="11" t="n">
         <v>219.47</v>
       </c>
-      <c r="J5" s="11" t="n">
-        <v>12509.8</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="11" t="n">
+        <v>20315.6</v>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t>断货高危</t>
         </is>
@@ -3448,19 +3460,22 @@
       <c r="G6" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="H6" s="13" t="n">
-        <v>55</v>
+      <c r="H6" s="11" t="n">
+        <v>66</v>
       </c>
       <c r="I6" s="11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="K6" s="11" t="n">
         <v>35.4</v>
       </c>
-      <c r="J6" s="11" t="n">
-        <v>1947</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="L6" s="11" t="n">
+        <v>3206.1</v>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3492,19 +3507,22 @@
       <c r="G7" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>55</v>
+      <c r="H7" s="11" t="n">
+        <v>66</v>
       </c>
       <c r="I7" s="11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="K7" s="11" t="n">
         <v>84.06999999999999</v>
       </c>
-      <c r="J7" s="11" t="n">
-        <v>4623.8</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="L7" s="11" t="n">
+        <v>7613.9</v>
+      </c>
+      <c r="M7" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3536,19 +3554,22 @@
       <c r="G8" s="11" t="n">
         <v>36.7</v>
       </c>
-      <c r="H8" s="13" t="n">
-        <v>43</v>
+      <c r="H8" s="11" t="n">
+        <v>54</v>
       </c>
       <c r="I8" s="11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="K8" s="11" t="n">
         <v>331.86</v>
       </c>
-      <c r="J8" s="11" t="n">
-        <v>14270</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="L8" s="11" t="n">
+        <v>23927.1</v>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3580,19 +3601,22 @@
       <c r="G9" s="11" t="n">
         <v>42.9</v>
       </c>
-      <c r="H9" s="13" t="n">
-        <v>32</v>
+      <c r="H9" s="11" t="n">
+        <v>42</v>
       </c>
       <c r="I9" s="11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" s="11" t="n">
         <v>192.04</v>
       </c>
-      <c r="J9" s="11" t="n">
-        <v>6145.3</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="L9" s="15" t="inlineStr">
+      <c r="L9" s="11" t="n">
+        <v>10491.8</v>
+      </c>
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3624,19 +3648,22 @@
       <c r="G10" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="H10" s="13" t="n">
-        <v>25</v>
+      <c r="H10" s="11" t="n">
+        <v>36</v>
       </c>
       <c r="I10" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="K10" s="11" t="n">
         <v>84.06999999999999</v>
       </c>
-      <c r="J10" s="11" t="n">
-        <v>2101.8</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="L10" s="15" t="inlineStr">
+      <c r="L10" s="11" t="n">
+        <v>3732.7</v>
+      </c>
+      <c r="M10" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3668,19 +3695,22 @@
       <c r="G11" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="H11" s="13" t="n">
-        <v>22</v>
+      <c r="H11" s="11" t="n">
+        <v>30</v>
       </c>
       <c r="I11" s="11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="K11" s="11" t="n">
         <v>138.05</v>
       </c>
-      <c r="J11" s="11" t="n">
-        <v>3037.1</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="L11" s="15" t="inlineStr">
+      <c r="L11" s="11" t="n">
+        <v>5268.9</v>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3712,19 +3742,22 @@
       <c r="G12" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="H12" s="13" t="n">
-        <v>19</v>
+      <c r="H12" s="11" t="n">
+        <v>30</v>
       </c>
       <c r="I12" s="11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="K12" s="11" t="n">
         <v>155.75</v>
       </c>
-      <c r="J12" s="11" t="n">
-        <v>2959.2</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="11" t="n">
+        <v>5477.2</v>
+      </c>
+      <c r="M12" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3756,19 +3789,22 @@
       <c r="G13" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="H13" s="13" t="n">
-        <v>17</v>
+      <c r="H13" s="11" t="n">
+        <v>30</v>
       </c>
       <c r="I13" s="11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="K13" s="11" t="n">
         <v>421.24</v>
       </c>
-      <c r="J13" s="11" t="n">
-        <v>7161.1</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="L13" s="11" t="n">
+        <v>13971.1</v>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
         <is>
           <t>紧急补货</t>
         </is>
@@ -3800,19 +3836,22 @@
       <c r="G14" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="H14" s="13" t="n">
-        <v>6</v>
+      <c r="H14" s="11" t="n">
+        <v>18</v>
       </c>
       <c r="I14" s="11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="K14" s="11" t="n">
         <v>144.09</v>
       </c>
-      <c r="J14" s="11" t="n">
-        <v>864.5</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="L14" s="11" t="n">
+        <v>2262.2</v>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3844,19 +3883,22 @@
       <c r="G15" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="H15" s="13" t="n">
-        <v>5</v>
+      <c r="H15" s="11" t="n">
+        <v>18</v>
       </c>
       <c r="I15" s="11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" s="11" t="n">
         <v>179.91</v>
       </c>
-      <c r="J15" s="11" t="n">
-        <v>899.5</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="L15" s="11" t="n">
+        <v>2644.7</v>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3888,55 +3930,249 @@
       <c r="G16" s="11" t="n">
         <v>140</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>216.81</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>B0HBB4L2SL</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>1EMO4510</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>172.41</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>942.5</v>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>B0HBBHJGXG</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>1EMO4220</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J18" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="11" t="n">
-        <v>216.81</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>867.2</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="K18" s="11" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>186</v>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr"/>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>B0HBB9X8RT</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>1EMO4530</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>B0HBBL8N35</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>1EMO4080</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>240</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>609</v>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr"/>
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr"/>
-      <c r="D17" s="17" t="n">
-        <v>90</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>143</v>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-      <c r="H17" s="17" t="n">
-        <v>397</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr"/>
-      <c r="J17" s="17" t="n">
-        <v>65658.7</v>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v>397</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr"/>
+      <c r="C21" s="17" t="inlineStr"/>
+      <c r="D21" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>193</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="17" t="n">
+        <v>582</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>703</v>
+      </c>
+      <c r="K21" s="17" t="inlineStr"/>
+      <c r="L21" s="17" t="n">
+        <v>117199.2</v>
+      </c>
+      <c r="M21" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3965,11 +4201,11 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>零动销新品 35 个 ｜ 占用在库+在途 615 件 ｜ 占用金额 ¥86,366</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>零动销新品 35 个（不备货）｜ 占用在库+在途 615 件 ｜ ¥86,366</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -5255,11 +5491,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5277,225 +5513,243 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>库存明细报表(33) 快照 2026-10-16（商品状态=推新 70个）+ 运营综合分析明细(48) 新品到货后约1个月销量</t>
+          <t>库存明细报表(33) 快照 2026-10-16（商品状态=推新 70个）+ 运营综合分析明细(48)（新品到货后约1个月销量）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>测算口径</t>
+          <t>匹配结果</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>目标库存 = 月销量 × 6；建议发货 = max(0, 目标库存 − (可用库存 + 头程在途))</t>
+          <t>ASIN 一一对应，交集 70/70</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>补货周期 / 安全库存</t>
+          <t>★ 任务性质</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>97 天 / 21 天（合计覆盖 118 天）</t>
+          <t>本地仓无库存 → 本表为【向工厂备货量】，不是从本地仓发货量</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr"/>
-      <c r="B6" s="20" t="inlineStr"/>
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>备货口径</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>备货数量 = 目标库存(月销×6) + 补货周期(97天)内消耗 − (可用库存 + 头程在途)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>新品ASIN总数</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="n">
-        <v>70</v>
+          <t>补货周期</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>97 天 = 采购30 + 海运60 + 入仓7 ｜ 安全库存 21 天（合计覆盖 118 天）</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　有销量</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="n">
-        <v>35</v>
-      </c>
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">　零动销</t>
+          <t>新品ASIN总数</t>
         </is>
       </c>
       <c r="B9" s="20" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　有销量</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
         <v>35</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr"/>
-      <c r="B10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>月销量合计（件）</t>
+          <t xml:space="preserve">　零动销</t>
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>118</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>库存合计（可用+在途）</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n">
-        <v>1118</v>
-      </c>
+      <c r="A12" s="19" t="inlineStr"/>
+      <c r="B12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>目标库存合计</t>
+          <t>月销量合计（件）</t>
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>708</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>整体库销比</t>
+          <t>在库+在途合计</t>
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>4.26</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr"/>
-      <c r="B15" s="20" t="inlineStr"/>
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>目标库存合计</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>708</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>需发货 ASIN</t>
+          <t>整体库销比</t>
         </is>
       </c>
       <c r="B16" s="20" t="n">
-        <v>13</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>需发货总件数</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>397</v>
-      </c>
+      <c r="A17" s="19" t="inlineStr"/>
+      <c r="B17" s="20" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>需发货总金额</t>
+          <t>★ 需备货 ASIN</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>¥65,659</t>
+          <t>17 个</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>需发货总箱数</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="n">
-        <v>397</v>
+          <t>★ 备货数量合计</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>703 件</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr"/>
-      <c r="B20" s="20" t="inlineStr"/>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>★ 备货金额合计</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>¥117,199</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>断货高危（&lt;30天）</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="n">
-        <v>2</v>
-      </c>
+      <c r="A21" s="19" t="inlineStr"/>
+      <c r="B21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>紧急补货（30-97天）</t>
+          <t>断货高危（可售&lt;30天）</t>
         </is>
       </c>
       <c r="B22" s="20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>偏低（97-118天）</t>
+          <t>紧急补货（可售30-97天）</t>
         </is>
       </c>
       <c r="B23" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>正常（&gt;118天）</t>
+          <t>偏低（97-118天）</t>
         </is>
       </c>
       <c r="B24" s="20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
+          <t>正常（&gt;118天）</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
           <t>零动销</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B26" s="20" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr"/>
-      <c r="B26" s="20" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>⚠ 结构错配提示</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>总量充足（库存 1118 件 &gt; 目标 708 件），但零动销积压 615 件 / ¥86,366，同时 13 个动销品缺 397 件 —— 建议调拨或清理滞销后再补货</t>
+      <c r="A27" s="19" t="inlineStr"/>
+      <c r="B27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>⚠ 结构提示</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>在库+在途 1118 件 &gt; 目标 708 件（总量够），但 35 个零动销压 615 件（¥86,366），同时 17 个动销品仍需备货 703 件 —— 建议先调拨/清理滞销</t>
         </is>
       </c>
     </row>
